--- a/basedatos_partidas/salida/descompuestos/CT-08-03-020.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-08-03-020.xlsx
@@ -565,10 +565,10 @@
         <v>13</v>
       </c>
       <c r="G11" t="n">
-        <v>0.22</v>
+        <v>0.225</v>
       </c>
       <c r="H11" t="n">
-        <v>2.86</v>
+        <v>2.93</v>
       </c>
     </row>
     <row r="12">
@@ -682,7 +682,7 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>28.46</v>
+        <v>28.53</v>
       </c>
     </row>
     <row r="17">
@@ -854,7 +854,7 @@
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>37.86</v>
+        <v>37.93</v>
       </c>
       <c r="H26" t="n">
         <v>0.38</v>
@@ -873,7 +873,7 @@
       </c>
       <c r="G27" s="4" t="n"/>
       <c r="H27" s="5" t="n">
-        <v>38.24</v>
+        <v>38.31</v>
       </c>
     </row>
   </sheetData>

--- a/basedatos_partidas/salida/descompuestos/CT-08-03-020.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-08-03-020.xlsx
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A3:H27"/>
+  <dimension ref="A1:H27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -451,6 +451,20 @@
     <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Capítulo: 08 Pisos y pavimentos</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Subcapítulo: Pisos de piedra natural y granito</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>

--- a/basedatos_partidas/salida/descompuestos/CT-08-03-020.xlsx
+++ b/basedatos_partidas/salida/descompuestos/CT-08-03-020.xlsx
@@ -784,7 +784,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MO-OF1-SOL</t>
+          <t>MO-OF1-PISO</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Oficial de 1ª solador.</t>
+          <t>Oficial de 1ª colocador de pisos.</t>
         </is>
       </c>
       <c r="F22" t="n">
